--- a/data/volleyball/calendrier_volleyP2.xlsx
+++ b/data/volleyball/calendrier_volleyP2.xlsx
@@ -4865,12 +4865,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ECL (1)|M__ENTPE (2)|M__VBMA2PA</t>
+          <t>ECL (3)|M__LYON 1 (9)|M__VBMA3PA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VBMA2PA</t>
+          <t>VBMA3PA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4890,17 +4890,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ECL (1)</t>
+          <t>ECL (3)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>ENTPE</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>ENTPE (2)</t>
+          <t>LYON 1 (9)</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -4930,52 +4930,40 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ECL (3)|M__LYON 1 (9)|M__VBMA3PA</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>VBMA3PA</t>
-        </is>
-      </c>
+          <t>UDG (1)|F__UDL (2)|F__</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ECL</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>EXTERNE</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ECL (3)</t>
+          <t>EXTERNE</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>LYON 1</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>EXTERNE</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>LYON 1 (9)</t>
+          <t>EXTERNE</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -4983,19 +4971,19 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>GRENOBLE</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>UDG (1)|F__UDL (2)|F__</t>
+          <t>UDL (1)|F__INSA (1)|F__</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -5017,10 +5005,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>EXTERNE</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>INSA</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
           <t>F</t>
@@ -5028,7 +5020,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>EXTERNE</t>
+          <t>INSA (1)</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -5036,28 +5028,36 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>GRENOBLE</t>
+          <t>BESSON</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>UDL (1)|F__INSA (1)|F__</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>INSA (2)|F__LYON 1 (11)|F__VBFA1PA</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>VBFA1PA</t>
+        </is>
+      </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>EXTERNE</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>INSA</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>F</t>
@@ -5065,17 +5065,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>EXTERNE</t>
+          <t>INSA (2)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>INSA</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>INSA (1)</t>
+          <t>LYON 1 (11)</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -5105,52 +5105,52 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>INSA (2)|F__LYON 1 (11)|F__VBFA1PA</t>
+          <t>LYON 1 (14)|M__ESME (2)|M__VBMA4PA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>VBFA1PA</t>
+          <t>VBMA4PA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>INSA</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>LYON 1 (14)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>ESME</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>INSA (2)</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>LYON 1</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>LYON 1 (11)</t>
+          <t>ESME (2)</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -5170,22 +5170,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>LYON 1 (14)|M__ESME (2)|M__VBMA4PA</t>
+          <t>ECL (1)|M__ENTPE (2)|M__VBMA2PA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>VBMA4PA</t>
+          <t>VBMA2PA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>LYON 1 (14)</t>
+          <t>ECL (1)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>ESME</t>
+          <t>ENTPE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>ESME (2)</t>
+          <t>ENTPE (2)</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -5228,59 +5228,59 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>ECL</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>LYON 1 (7)|F__ESSCA (1)|F__VBFA4PA</t>
+          <t>ENS (1)|M__INSA (2)|M__VBMA1PB</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>VBFA4PA</t>
+          <t>VBMA1PB</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>ENS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>LYON 1 (7)</t>
+          <t>ENS (1)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ESSCA</t>
+          <t>INSA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>ESSCA (1)</t>
+          <t>INSA (2)</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -5288,56 +5288,56 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
+          <t>BESSON</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ENS (1)|M__INSA (2)|M__VBMA1PB</t>
+          <t>LYON 1 (5)|M__ISARA (1)|M__VBMA2PB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>VBMA1PB</t>
+          <t>VBMA2PB</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ENS</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>LYON 1 (5)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ISARA</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>ENS (1)</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>INSA</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="I77" t="inlineStr">
         <is>
           <t>M</t>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>INSA (2)</t>
+          <t>ISARA (1)</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -5365,12 +5365,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>LYON 1 (5)|M__ISARA (1)|M__VBMA2PB</t>
+          <t>LYON 1 (25)|M__ESSCA (1)|M__VBMA4PB</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>VBMA2PB</t>
+          <t>VBMA4PB</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5390,12 +5390,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>LYON 1 (5)</t>
+          <t>LYON 1 (25)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ISARA</t>
+          <t>ESSCA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>ISARA (1)</t>
+          <t>ESSCA (1)</t>
         </is>
       </c>
       <c r="K78" t="n">
@@ -5430,12 +5430,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>LYON 1 (25)|M__ESSCA (1)|M__VBMA4PB</t>
+          <t>LYON 1 (5)|F__LYON 2 (6)|F__VBFA2PA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>VBMA4PB</t>
+          <t>VBFA2PA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5445,37 +5445,37 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>LYON 1 (25)</t>
+          <t>LYON 1 (5)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>ESSCA</t>
+          <t>LYON 2</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>ESSCA (1)</t>
+          <t>LYON 2 (6)</t>
         </is>
       </c>
       <c r="K79" t="n">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5495,22 +5495,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ESME (2)|F__ISOSTEO (1)|F__VBFA4PB</t>
+          <t>LYON 1 (9)|F__LYON 2 (5)|F__VBFA3PA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>VBFA4PB</t>
+          <t>VBFA3PA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ESME</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5520,17 +5520,17 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ESME (2)</t>
+          <t>LYON 1 (9)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>ISOSTEO</t>
+          <t>LYON 2</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>ISOSTEO (1)</t>
+          <t>LYON 2 (5)</t>
         </is>
       </c>
       <c r="K80" t="n">
@@ -5548,64 +5548,64 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
+          <t>BESSON</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>LYON 1 (5)|F__LYON 2 (6)|F__VBFA2PA</t>
+          <t>ESA (1)|M__CPE (1)|M__VBMA2PD</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>VBFA2PA</t>
+          <t>VBMA2PD</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>ESA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>LYON 1 (5)</t>
+          <t>ESA (1)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>LYON 2</t>
+          <t>CPE</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>LYON 2 (6)</t>
+          <t>CPE (1)</t>
         </is>
       </c>
       <c r="K81" t="n">
@@ -5618,29 +5618,29 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>ESA</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>LYON 1 (9)|F__LYON 2 (5)|F__VBFA3PA</t>
+          <t>SANTE (5)|F__CPE (1)|F__VBFA3PB</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VBFA3PA</t>
+          <t>VBFA3PB</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>SANTE</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5650,17 +5650,17 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>LYON 1 (9)</t>
+          <t>SANTE (5)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>LYON 2</t>
+          <t>CPE</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>LYON 2 (5)</t>
+          <t>CPE (1)</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -5683,59 +5683,59 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>L. J. HAUT</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CESI (2)|M__LYON 1 (17)|M__VBMA3PE</t>
+          <t>LYON 2 (7)|F__SANTE (3)|F__VBFA3PC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>VBMA3PE</t>
+          <t>VBFA3PC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CESI</t>
+          <t>LYON 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CESI (2)</t>
+          <t>LYON 2 (7)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>SANTE</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>LYON 1 (17)</t>
+          <t>SANTE (3)</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -5748,24 +5748,24 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>LAENNEC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ESA (1)|M__CPE (1)|M__VBMA2PD</t>
+          <t>LYON 3 (1)|M__LYON 2 (2)|M__VBMA1PC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VBMA2PD</t>
+          <t>VBMA1PC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ESA</t>
+          <t>LYON 3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5780,17 +5780,17 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ESA (1)</t>
+          <t>LYON 3 (1)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>LYON 2</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>CPE (1)</t>
+          <t>LYON 2 (2)</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -5813,24 +5813,24 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>ESA</t>
+          <t>LAENNEC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SANTE (5)|F__CPE (1)|F__VBFA3PB</t>
+          <t>LYON 3 (5)|M__LYON 1 (23)|M__VBMA4PC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>VBFA3PB</t>
+          <t>VBMA4PC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SANTE</t>
+          <t>LYON 3</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5840,32 +5840,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>SANTE (5)</t>
+          <t>LYON 3 (5)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>CPE (1)</t>
+          <t>LYON 1 (23)</t>
         </is>
       </c>
       <c r="K85" t="n">
@@ -5878,94 +5878,94 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>L. J. HAUT</t>
+          <t>LAENNEC</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LYON 2 (7)|F__SANTE (3)|F__VBFA3PC</t>
+          <t>INSA (3)|M__LYON 1 (8)|M__VBMA2PA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>VBFA3PC</t>
+          <t>VBMA2PA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LYON 2</t>
+          <t>INSA</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>LYON 2 (7)</t>
+          <t>INSA (3)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SANTE</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>SANTE (3)</t>
+          <t>LYON 1 (8)</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
+          <t>BESSON</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>LYON 3 (1)|M__LYON 2 (2)|M__VBMA1PC</t>
+          <t>LYON 1 (13)|M__INSA (6)|M__VBMA3PA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>VBMA1PC</t>
+          <t>VBMA3PA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>LYON 3</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5975,17 +5975,17 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>LYON 3 (1)</t>
+          <t>LYON 1 (13)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>LYON 2</t>
+          <t>INSA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5995,42 +5995,42 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>LYON 2 (2)</t>
+          <t>INSA (6)</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
+          <t>BESSON</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>LYON 3 (5)|M__LYON 1 (23)|M__VBMA4PC</t>
+          <t>LYON 1 (27)|M__LYON 1 (14)|M__VBMA4PA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VBMA4PC</t>
+          <t>VBMA4PA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>LYON 3</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>LYON 3 (5)</t>
+          <t>LYON 1 (27)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6060,32 +6060,32 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>LYON 1 (23)</t>
+          <t>LYON 1 (14)</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
+          <t>BESSON</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>INSA (3)|M__LYON 1 (8)|M__VBMA2PA</t>
+          <t>INSA (1)|M__LYON 1 (1)|M__VBMA1PA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VBMA2PA</t>
+          <t>VBMA1PA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>INSA (3)</t>
+          <t>INSA (1)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>LYON 1 (8)</t>
+          <t>LYON 1 (1)</t>
         </is>
       </c>
       <c r="K89" t="n">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -6145,12 +6145,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>LYON 1 (13)|M__INSA (6)|M__VBMA3PA</t>
+          <t>LYON 1 (3)|M__INSA (4)|M__VBMA2PB</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VBMA3PA</t>
+          <t>VBMA2PB</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>LYON 1 (13)</t>
+          <t>LYON 1 (3)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>INSA (6)</t>
+          <t>INSA (4)</t>
         </is>
       </c>
       <c r="K90" t="n">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -6210,12 +6210,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>LYON 1 (14)|M__LYON 1 (27)|M__VBMA4PA</t>
+          <t>LYON 1 (9)|M__INSA (5)|M__VBMA3PA</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VBMA4PA</t>
+          <t>VBMA3PA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6235,17 +6235,17 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>LYON 1 (14)</t>
+          <t>LYON 1 (9)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>INSA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>LYON 1 (27)</t>
+          <t>INSA (5)</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -6275,17 +6275,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>INSA (1)|M__LYON 1 (1)|M__VBMA1PA</t>
+          <t>ESSCA (1)|F__LYON 1 (13)|F__VBFA4PA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VBMA1PA</t>
+          <t>VBFA4PA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>INSA</t>
+          <t>ESSCA</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>INSA (1)</t>
+          <t>ESSCA (1)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6310,17 +6310,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>LYON 1 (1)</t>
+          <t>LYON 1 (13)</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -6333,59 +6333,59 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>L. J. HAUT</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LYON 1 (3)|M__INSA (4)|M__VBMA2PB</t>
+          <t>INSA (1)|F__EML (1)|F__VBFA1PA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VBMA2PB</t>
+          <t>VBFA1PA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>INSA</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>LYON 1 (3)</t>
+          <t>INSA (1)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>INSA</t>
+          <t>EML</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>INSA (4)</t>
+          <t>EML (1)</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -6405,42 +6405,42 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LYON 1 (9)|M__INSA (5)|M__VBMA3PA</t>
+          <t>LYON 2 (6)|M__LYON 1 (12)|M__VBMA3PC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VBMA3PA</t>
+          <t>VBMA3PC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
+          <t>LYON 2</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>LYON 2 (6)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
           <t>LYON 1</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>LYON 1 (9)</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>INSA</t>
-        </is>
-      </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>INSA (5)</t>
+          <t>LYON 1 (12)</t>
         </is>
       </c>
       <c r="K94" t="n">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -6470,32 +6470,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>LYON 1 (13)|F__ESSCA (1)|F__VBFA4PA</t>
+          <t>ISOSTEO (1)|M__ESSCA (1)|M__VBMA4PB</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VBFA4PA</t>
+          <t>VBMA4PB</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>ISOSTEO</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>LYON 1 (13)</t>
+          <t>ISOSTEO (1)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6523,44 +6523,44 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>L. J. HAUT</t>
+          <t>BESSON</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>INSA (1)|F__EML (1)|F__VBFA1PA</t>
+          <t>ENS (3)|M__EML (2)|M__VBMA3PC</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>VBFA1PA</t>
+          <t>VBMA3PC</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>INSA</t>
+          <t>ENS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>INSA (1)</t>
+          <t>ENS (3)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -6570,17 +6570,17 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>EML (1)</t>
+          <t>EML (2)</t>
         </is>
       </c>
       <c r="K96" t="n">
@@ -6593,29 +6593,29 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>DESCARTES</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LYON 2 (6)|M__LYON 1 (12)|M__VBMA3PC</t>
+          <t>CATHO (1)|M__CESI (1)|M__VBMA3PD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>VBMA3PC</t>
+          <t>VBMA3PD</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>LYON 2</t>
+          <t>CATHO</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6625,17 +6625,17 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>LYON 2 (6)</t>
+          <t>CATHO (1)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>CESI</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>LYON 1 (12)</t>
+          <t>CESI (1)</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -6658,59 +6658,59 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>LAENNEC</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ESSCA (1)|M__ISOSTEO (1)|M__VBMA4PB</t>
+          <t>LYON 3 (2)|F__LYON 1 (2)|F__VBFA2PC</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VBMA4PB</t>
+          <t>VBFA2PC</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ESSCA</t>
+          <t>LYON 3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>ESSCA (1)</t>
+          <t>LYON 3 (2)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>ISOSTEO</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>ISOSTEO (1)</t>
+          <t>LYON 1 (2)</t>
         </is>
       </c>
       <c r="K98" t="n">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -6730,52 +6730,52 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ENS (3)|M__EML (2)|M__VBMA3PC</t>
+          <t>CATHO (1)|F__LYON 1 (3)|F__VBFA3PC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>VBMA3PC</t>
+          <t>VBFA3PC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ENS</t>
+          <t>CATHO</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>CATHO (1)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>LYON 1</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>ENS (3)</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>EML</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>EML (2)</t>
+          <t>LYON 1 (3)</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -6783,29 +6783,29 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>DESCARTES</t>
+          <t>BESSON</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CATHO (1)|M__CESI (1)|M__VBMA3PD</t>
+          <t>EML (1)|M__ECAM (1)|M__VBMA1PC</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>VBMA3PD</t>
+          <t>VBMA1PC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CATHO</t>
+          <t>EML</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CATHO (1)</t>
+          <t>EML (1)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>CESI</t>
+          <t>ECAM</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>CESI (1)</t>
+          <t>ECAM (1)</t>
         </is>
       </c>
       <c r="K100" t="n">
@@ -6848,34 +6848,34 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
+          <t>BESSON</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LYON 3 (2)|F__LYON 1 (2)|F__VBFA2PC</t>
+          <t>ENS (1)|F__LYON 1 (4)|F__VBFA2PB</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>VBFA2PC</t>
+          <t>VBFA2PB</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>LYON 3</t>
+          <t>ENS</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>LYON 3 (2)</t>
+          <t>ENS (1)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>LYON 1 (2)</t>
+          <t>LYON 1 (4)</t>
         </is>
       </c>
       <c r="K101" t="n">
@@ -6918,51 +6918,51 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>DESCARTES</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CATHO (1)|F__LYON 1 (3)|F__VBFA3PC</t>
+          <t>LYON 2 (5)|F__ECAM (1)|F__VBFA3PA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>VBFA3PC</t>
+          <t>VBFA3PA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CATHO</t>
+          <t>LYON 2</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>LYON 2 (5)</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>ECAM</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>CATHO (1)</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>LYON 1</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="I102" t="inlineStr">
         <is>
           <t>F</t>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>LYON 1 (3)</t>
+          <t>ECAM (1)</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -6983,59 +6983,59 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>L. J. HAUT</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EML (1)|M__ECAM (1)|M__VBMA1PC</t>
+          <t>LYON 3 (5)|F__EML (2)|F__VBFA4PC</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>VBMA1PC</t>
+          <t>VBFA4PC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
+          <t>LYON 3</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>LYON 3 (5)</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
           <t>EML</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>EML (1)</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>ECAM</t>
-        </is>
-      </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>ECAM (1)</t>
+          <t>EML (2)</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -7048,59 +7048,59 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>LAENNEC</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ENS (1)|F__LYON 1 (4)|F__VBFA2PB</t>
+          <t>LYON 3 (3)|M__VETO (1)|M__VBMA2PE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>VBFA2PB</t>
+          <t>VBMA2PE</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ENS</t>
+          <t>LYON 3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>LYON 3 (3)</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>VETO</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>ENS (1)</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>LYON 1</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>LYON 1 (4)</t>
+          <t>VETO (1)</t>
         </is>
       </c>
       <c r="K104" t="n">
@@ -7113,59 +7113,59 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>DESCARTES</t>
+          <t>LAENNEC</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>LYON 2 (5)|F__ECAM (1)|F__VBFA3PA</t>
+          <t>SANTE (5)|M__LYON 2 (5)|M__VBMA4PC</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>VBFA3PA</t>
+          <t>VBMA4PC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
+          <t>SANTE</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>SANTE (5)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
           <t>LYON 2</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
         <is>
           <t>LYON 2 (5)</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>ECAM</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>ECAM (1)</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -7178,29 +7178,29 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>L. J. HAUT</t>
+          <t>LAENNEC</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LYON 3 (5)|F__EML (2)|F__VBFA4PC</t>
+          <t>LYON 1 (11)|F__ENTPE (1)|F__VBFA1PA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>VBFA4PC</t>
+          <t>VBFA1PA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>LYON 3</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7210,17 +7210,17 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>LYON 3 (5)</t>
+          <t>LYON 1 (11)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>EML</t>
+          <t>ENTPE</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7230,37 +7230,37 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>EML (2)</t>
+          <t>ENTPE (1)</t>
         </is>
       </c>
       <c r="K106" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
+          <t>BESSON</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>LYON 3 (3)|M__VETO (1)|M__VBMA2PE</t>
+          <t>INSA (3)|F__LYON 1 (5)|F__VBFA2PA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>VBMA2PE</t>
+          <t>VBFA2PA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LYON 3</t>
+          <t>INSA</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -7270,142 +7270,142 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>LYON 3 (3)</t>
+          <t>INSA (3)</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>VETO</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>VETO (1)</t>
+          <t>LYON 1 (5)</t>
         </is>
       </c>
       <c r="K107" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
+          <t>BESSON</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SANTE (5)|M__LYON 2 (5)|M__VBMA4PC</t>
+          <t>LYON 1 (7)|F__LYON 1 (12)|F__VBFA4PA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>VBMA4PC</t>
+          <t>VBFA4PA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SANTE</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SANTE (5)</t>
+          <t>LYON 1 (7)</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>LYON 2</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>LYON 2 (5)</t>
+          <t>LYON 1 (12)</t>
         </is>
       </c>
       <c r="K108" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
+          <t>BESSON</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>LYON 1 (11)|F__ENTPE (1)|F__VBFA1PA</t>
+          <t>ECL (2)|M__ENTPE (2)|M__VBMA2PA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>VBFA1PA</t>
+          <t>VBMA2PA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>LYON 1 (11)</t>
+          <t>ECL (2)</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -7415,17 +7415,17 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>ENTPE (1)</t>
+          <t>ENTPE (2)</t>
         </is>
       </c>
       <c r="K109" t="n">
@@ -7438,49 +7438,41 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>ECL</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>INSA (3)|F__LYON 1 (5)|F__VBFA2PA</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>VBFA2PA</t>
-        </is>
-      </c>
+          <t>UCA (1)|F__INSA (1)|F__</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
+          <t>EXTERNE</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>EXTERNE</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
           <t>INSA</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>INSA (3)</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>LYON 1</t>
-        </is>
-      </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7490,7 +7482,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>LYON 1 (5)</t>
+          <t>INSA (1)</t>
         </is>
       </c>
       <c r="K110" t="n">
@@ -7498,36 +7490,28 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>CLERMONT</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>LYON 1 (7)|F__LYON 1 (12)|F__VBFA4PA</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>VBFA4PA</t>
-        </is>
-      </c>
+          <t>UDG (1)|F__UDL (1)|F__</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>LYON 1</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>EXTERNE</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>F</t>
@@ -7535,19 +7519,15 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>LYON 1 (7)</t>
+          <t>EXTERNE</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>LYON 1</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>EXTERNE</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>F</t>
@@ -7555,7 +7535,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>LYON 1 (12)</t>
+          <t>EXTERNE</t>
         </is>
       </c>
       <c r="K111" t="n">
@@ -7563,36 +7543,28 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>GRENOBLE</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ECL (2)|M__ENTPE (2)|M__VBMA2PA</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>VBMA2PA</t>
-        </is>
-      </c>
+          <t>UDG (1)|M__INSA (1)|M__</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ECL</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>EXTERNE</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>M</t>
@@ -7600,17 +7572,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>ECL (2)</t>
+          <t>EXTERNE</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>ENTPE</t>
+          <t>INSA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7620,7 +7592,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>ENTPE (2)</t>
+          <t>INSA (1)</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -7628,41 +7600,49 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>GRENOBLE</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>UCA (1)|F__INSA (1)|F__</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
+          <t>INSA (2)|M__LYON 2 (1)|M__VBMA1PB</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>VBMA1PB</t>
+        </is>
+      </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>EXTERNE</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
+          <t>INSA</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>EXTERNE</t>
+          <t>INSA (2)</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>INSA</t>
+          <t>LYON 2</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7672,12 +7652,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>INSA (1)</t>
+          <t>LYON 2 (1)</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -7685,28 +7665,36 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>CLERMONT</t>
+          <t>BESSON</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>UDG (1)|F__UDL (1)|F__</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr"/>
+          <t>ESSCA (1)|F__ECL (2)|F__VBFA4PA</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>VBFA4PA</t>
+        </is>
+      </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>EXTERNE</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>ESSCA</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>F</t>
@@ -7714,15 +7702,19 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>EXTERNE</t>
+          <t>ESSCA (1)</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>EXTERNE</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr">
         <is>
           <t>F</t>
@@ -7730,7 +7722,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>EXTERNE</t>
+          <t>ECL (2)</t>
         </is>
       </c>
       <c r="K114" t="n">
@@ -7738,36 +7730,44 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>GRENOBLE</t>
+          <t>ECL</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>UDG (1)|M__INSA (1)|M__</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>EML (1)|F__INSA (2)|F__VBFA1PA</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>VBFA1PA</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>EXTERNE</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>EML</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>EXTERNE</t>
+          <t>EML (1)</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -7777,17 +7777,17 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>INSA (1)</t>
+          <t>INSA (2)</t>
         </is>
       </c>
       <c r="K115" t="n">
@@ -7795,34 +7795,34 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>GRENOBLE</t>
+          <t>BESSON</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>INSA (2)|M__LYON 2 (1)|M__VBMA1PB</t>
+          <t>LYON 1 (15)|M__LYON 1 (22)|M__VBMA3PD</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>VBMA1PB</t>
+          <t>VBMA3PD</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>INSA</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7832,17 +7832,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>INSA (2)</t>
+          <t>LYON 1 (15)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>LYON 2</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>LYON 2 (1)</t>
+          <t>LYON 1 (22)</t>
         </is>
       </c>
       <c r="K116" t="n">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -7872,52 +7872,52 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ESSCA (1)|F__ECL (2)|F__VBFA4PA</t>
+          <t>LYON 1 (19)|M__ISOSTEO (1)|M__VBMA4PB</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>VBFA4PA</t>
+          <t>VBMA4PB</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ESSCA</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>LYON 1 (19)</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>ISOSTEO</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>ESSCA (1)</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>ECL</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>ECL (2)</t>
+          <t>ISOSTEO (1)</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -7925,56 +7925,56 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>BESSON</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EML (1)|F__INSA (2)|F__VBFA1PA</t>
+          <t>ESME (2)|F__ISOSTEO (1)|F__VBFA4PB</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>VBFA1PA</t>
+          <t>VBFA4PB</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>EML</t>
+          <t>ESME</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>ESME (2)</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>ISOSTEO</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>EML (1)</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>INSA</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="I118" t="inlineStr">
         <is>
           <t>F</t>
@@ -7982,7 +7982,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>INSA (2)</t>
+          <t>ISOSTEO (1)</t>
         </is>
       </c>
       <c r="K118" t="n">
@@ -7995,19 +7995,19 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>LYON 2 HC</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>LYON 1 (15)|M__LYON 1 (22)|M__VBMA3PD</t>
+          <t>LYON 1 (6)|F__LYON 3 (4)|F__VBFA3PB</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>VBMA3PD</t>
+          <t>VBFA3PB</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8017,37 +8017,37 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>LYON 1 (15)</t>
+          <t>LYON 1 (6)</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>LYON 3</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>LYON 1 (22)</t>
+          <t>LYON 3 (4)</t>
         </is>
       </c>
       <c r="K119" t="n">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -8067,42 +8067,42 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>LYON 1 (19)|M__ISOSTEO (1)|M__VBMA4PB</t>
+          <t>CESI (2)|M__LYON 1 (17)|M__VBMA3PE</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>VBMA4PB</t>
+          <t>VBMA3PE</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
+          <t>CESI</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>CESI (2)</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
           <t>LYON 1</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>LYON 1 (19)</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>ISOSTEO</t>
-        </is>
-      </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>ISOSTEO (1)</t>
+          <t>LYON 1 (17)</t>
         </is>
       </c>
       <c r="K120" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -8132,12 +8132,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>LYON 1 (2)|M__ENS (1)|M__VBMA1PB</t>
+          <t>LYON 1 (16)|M__SANTE (4)|M__VBMA3PF</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>VBMA1PB</t>
+          <t>VBMA3PF</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8157,17 +8157,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>LYON 1 (2)</t>
+          <t>LYON 1 (16)</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>ENS</t>
+          <t>SANTE</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>ENS (1)</t>
+          <t>SANTE (4)</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -8185,64 +8185,64 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>DESCARTES</t>
+          <t>BESSON</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>LYON 1 (6)|F__LYON 3 (4)|F__VBFA3PB</t>
+          <t>ESA (1)|M__SANTE (1)|M__VBMA2PD</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>VBFA3PB</t>
+          <t>VBMA2PD</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>ESA</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>LYON 1 (6)</t>
+          <t>ESA (1)</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>LYON 3</t>
+          <t>SANTE</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>LYON 3 (4)</t>
+          <t>SANTE (1)</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -8255,24 +8255,24 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>ESA</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SANTE (2)|M__LYON 1 (21)|M__VBMA2PE</t>
+          <t>ESA (2)|F__LYON 3 (6)|F__VBFA4PC</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>VBMA2PE</t>
+          <t>VBFA4PC</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SANTE</t>
+          <t>ESA</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -8282,32 +8282,32 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SANTE (2)</t>
+          <t>ESA (2)</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>LYON 3</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>LYON 1 (21)</t>
+          <t>LYON 3 (6)</t>
         </is>
       </c>
       <c r="K123" t="n">
@@ -8320,29 +8320,29 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>L. J. HAUT</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>LYON 1 (16)|M__SANTE (4)|M__VBMA3PF</t>
+          <t>LYON 3 (2)|M__CPE (1)|M__VBMA2PD</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>VBMA3PF</t>
+          <t>VBMA2PD</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>LYON 3</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8352,17 +8352,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>LYON 1 (16)</t>
+          <t>LYON 3 (2)</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SANTE</t>
+          <t>CPE</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>SANTE (4)</t>
+          <t>CPE (1)</t>
         </is>
       </c>
       <c r="K124" t="n">
@@ -8385,29 +8385,29 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>LAENNEC</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ESA (1)|M__SANTE (1)|M__VBMA2PD</t>
+          <t>SANTE (2)|M__LYON 1 (21)|M__VBMA2PE</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>VBMA2PD</t>
+          <t>VBMA2PE</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ESA</t>
+          <t>SANTE</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8417,17 +8417,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>ESA (1)</t>
+          <t>SANTE (2)</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SANTE</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>SANTE (1)</t>
+          <t>LYON 1 (21)</t>
         </is>
       </c>
       <c r="K125" t="n">
@@ -8450,24 +8450,24 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>ESA</t>
+          <t>LAENNEC</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ESA (2)|F__LYON 3 (6)|F__VBFA4PC</t>
+          <t>CATHO (2)|M__LYON 3 (4)|M__VBMA3PF</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>VBFA4PC</t>
+          <t>VBMA3PF</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ESA</t>
+          <t>CATHO</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ESA (2)</t>
+          <t>CATHO (2)</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -8492,17 +8492,17 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>LYON 3 (6)</t>
+          <t>LYON 3 (4)</t>
         </is>
       </c>
       <c r="K126" t="n">
@@ -8522,37 +8522,37 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>LYON 3 (2)|M__CPE (1)|M__VBMA2PD</t>
+          <t>LYON 2 (6)|F__ECL (1)|F__VBFA2PA</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>VBMA2PD</t>
+          <t>VBFA2PA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>LYON 3</t>
+          <t>LYON 2</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>LYON 3 (2)</t>
+          <t>LYON 2 (6)</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>CPE (1)</t>
+          <t>ECL (1)</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -8580,59 +8580,59 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
+          <t>LYON 2 HC</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CATHO (2)|M__LYON 3 (4)|M__VBMA3PF</t>
+          <t>LYON 2 (3)|F__VETO (1)|F__VBFA2PC</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>VBMA3PF</t>
+          <t>VBFA2PC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CATHO</t>
+          <t>LYON 2</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>CATHO (2)</t>
+          <t>LYON 2 (3)</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>LYON 3</t>
+          <t>VETO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>LYON 3 (4)</t>
+          <t>VETO (1)</t>
         </is>
       </c>
       <c r="K128" t="n">
@@ -8645,44 +8645,44 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
+          <t>LYON 2 HC</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>LYON 2 (6)|F__ECL (1)|F__VBFA2PA</t>
+          <t>LYON 2 (IEP) (4)|M__VETO (1)|M__VBMA2PE</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>VBFA2PA</t>
+          <t>VBMA2PE</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>LYON 2</t>
+          <t>LYON 2 (IEP)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>LYON 2 (6)</t>
+          <t>LYON 2 (IEP) (4)</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>VETO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8692,12 +8692,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>ECL (1)</t>
+          <t>VETO (1)</t>
         </is>
       </c>
       <c r="K129" t="n">
@@ -8717,22 +8717,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>LYON 2 (3)|F__VETO (1)|F__VBFA2PC</t>
+          <t>LYON 1 (1)|F__INSA (1)|F__VBFA1PA</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>VBFA2PC</t>
+          <t>VBFA1PA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>LYON 2</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>LYON 2 (3)</t>
+          <t>LYON 1 (1)</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>VETO</t>
+          <t>INSA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8762,42 +8762,42 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>VETO (1)</t>
+          <t>INSA (1)</t>
         </is>
       </c>
       <c r="K130" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>LYON 2 HC</t>
+          <t>BESSON</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>LYON 2 (IEP) (4)|M__VETO (1)|M__VBMA2PE</t>
+          <t>LYON 1 (26)|M__LYON 1 (1)|M__VBMA1PA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>VBMA2PE</t>
+          <t>VBMA1PA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>LYON 2 (IEP)</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>LYON 2 (IEP) (4)</t>
+          <t>LYON 1 (26)</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>VETO</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8827,37 +8827,37 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>VETO (1)</t>
+          <t>LYON 1 (1)</t>
         </is>
       </c>
       <c r="K131" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>LYON 2 HC</t>
+          <t>BESSON</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>LYON 1 (1)|F__INSA (1)|F__VBFA1PA</t>
+          <t>ENTPE (1)|M__INSA (1)|M__VBMA1PA</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>VBFA1PA</t>
+          <t>VBMA1PA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>ENTPE</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8867,12 +8867,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LYON 1 (1)</t>
+          <t>ENTPE (1)</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8912,22 +8912,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>LYON 1 (26)|M__LYON 1 (1)|M__VBMA1PA</t>
+          <t>INSA (3)|M__ECL (1)|M__VBMA2PA</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>VBMA1PA</t>
+          <t>VBMA2PA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>INSA</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>LYON 1 (26)</t>
+          <t>INSA (3)</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8957,7 +8957,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>LYON 1 (1)</t>
+          <t>ECL (1)</t>
         </is>
       </c>
       <c r="K133" t="n">
@@ -8970,29 +8970,29 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>ECL</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ENTPE (1)|M__INSA (1)|M__VBMA1PA</t>
+          <t>ECL (3)|M__INSA (6)|M__VBMA3PA</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>VBMA1PA</t>
+          <t>VBMA3PA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ENTPE</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>ENTPE (1)</t>
+          <t>ECL (3)</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>INSA (1)</t>
+          <t>INSA (6)</t>
         </is>
       </c>
       <c r="K134" t="n">
@@ -9035,29 +9035,29 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>ECL</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>INSA (3)|M__ECL (1)|M__VBMA2PA</t>
+          <t>CPE (2)|M__LYON 1 (10)|M__VBMA3PB</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>VBMA2PA</t>
+          <t>VBMA3PB</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>INSA</t>
+          <t>CPE</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -9067,17 +9067,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>INSA (3)</t>
+          <t>CPE (2)</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>ECL (1)</t>
+          <t>LYON 1 (10)</t>
         </is>
       </c>
       <c r="K135" t="n">
@@ -9095,34 +9095,34 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>BESSON</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ECL (3)|M__INSA (6)|M__VBMA3PA</t>
+          <t>ISARA (2)|M__LYON 1 (24)|M__VBMA3PB</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>VBMA3PA</t>
+          <t>VBMA3PB</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>ISARA</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -9132,17 +9132,17 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>ECL (3)</t>
+          <t>ISARA (2)</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>INSA</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>INSA (6)</t>
+          <t>LYON 1 (24)</t>
         </is>
       </c>
       <c r="K136" t="n">
@@ -9160,34 +9160,34 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>BESSON</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CPE (2)|M__LYON 1 (10)|M__VBMA3PB</t>
+          <t>LYON 1 (11)|M__ESSCA (1)|M__VBMA4PB</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>VBMA3PB</t>
+          <t>VBMA4PB</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CPE</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -9197,17 +9197,17 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>CPE (2)</t>
+          <t>LYON 1 (11)</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>ESSCA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>LYON 1 (10)</t>
+          <t>ESSCA (1)</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -9237,52 +9237,52 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ISARA (2)|M__LYON 1 (24)|M__VBMA3PB</t>
+          <t>LYON 1 (7)|F__ESSCA (1)|F__VBFA4PA</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>VBMA3PB</t>
+          <t>VBFA4PA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ISARA</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>ISARA (2)</t>
+          <t>LYON 1 (7)</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>ESSCA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>LYON 1 (24)</t>
+          <t>ESSCA (1)</t>
         </is>
       </c>
       <c r="K138" t="n">
@@ -9295,19 +9295,19 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>LYON 2 HC</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>LYON 1 (11)|M__ESSCA (1)|M__VBMA4PB</t>
+          <t>LYON 1 (10)|F__ISOSTEO (1)|F__VBFA4PB</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>VBMA4PB</t>
+          <t>VBFA4PB</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9317,22 +9317,22 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>LYON 1 (11)</t>
+          <t>LYON 1 (10)</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>ESSCA</t>
+          <t>ISOSTEO</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>ESSCA (1)</t>
+          <t>ISOSTEO (1)</t>
         </is>
       </c>
       <c r="K139" t="n">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -9367,7 +9367,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>LYON 1 (10)|F__ISOSTEO (1)|F__VBFA4PB</t>
+          <t>LYON 1 (8)|F__ESME (2)|F__VBFA4PB</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -9392,17 +9392,17 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>LYON 1 (10)</t>
+          <t>LYON 1 (8)</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>ISOSTEO</t>
+          <t>ESME</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>ISOSTEO (1)</t>
+          <t>ESME (2)</t>
         </is>
       </c>
       <c r="K140" t="n">
@@ -9432,52 +9432,52 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>LYON 1 (8)|F__ESME (2)|F__VBFA4PB</t>
+          <t>CESI (1)|M__LYON 1 (22)|M__VBMA3PD</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>VBFA4PB</t>
+          <t>VBMA3PD</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
+          <t>CESI</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>CESI (1)</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
           <t>LYON 1</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>LYON 1 (8)</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>ESME</t>
-        </is>
-      </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>ESME (2)</t>
+          <t>LYON 1 (22)</t>
         </is>
       </c>
       <c r="K141" t="n">
@@ -9497,44 +9497,44 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CESI (1)|M__LYON 1 (22)|M__VBMA3PD</t>
+          <t>LYON 1 (2)|M__ENS (1)|M__VBMA1PB</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>VBMA3PD</t>
+          <t>VBMA1PB</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CESI</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>LYON 1 (2)</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>ENS</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>CESI (1)</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>LYON 1</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="I142" t="inlineStr">
         <is>
           <t>M</t>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>LYON 1 (22)</t>
+          <t>ENS (1)</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>DESCARTES</t>
         </is>
       </c>
     </row>
@@ -10017,7 +10017,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>LYON 1 (1)|F__LYON 1 (11)|F__VBFA1PA</t>
+          <t>ENTPE (1)|F__INSA (2)|F__VBFA1PA</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>ENTPE</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -10042,17 +10042,17 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>LYON 1 (1)</t>
+          <t>ENTPE (1)</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>INSA</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>LYON 1 (11)</t>
+          <t>INSA (2)</t>
         </is>
       </c>
       <c r="K150" t="n">
@@ -10082,7 +10082,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ENTPE (1)|F__INSA (2)|F__VBFA1PA</t>
+          <t>LYON 1 (11)|F__LYON 1 (1)|F__VBFA1PA</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10092,34 +10092,34 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ENTPE</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>LYON 1 (11)</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>LYON 1</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>ENTPE (1)</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>INSA</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="I151" t="inlineStr">
         <is>
           <t>F</t>
@@ -10127,7 +10127,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>INSA (2)</t>
+          <t>LYON 1 (1)</t>
         </is>
       </c>
       <c r="K151" t="n">
@@ -11057,7 +11057,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>LYON 1 (16)|M__CATHO (2)|M__VBMA3PF</t>
+          <t>CATHO (2)|M__LYON 1 (16)|M__VBMA3PF</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11067,42 +11067,42 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
+          <t>CATHO</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>CATHO (2)</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
           <t>LYON 1</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="H166" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
         <is>
           <t>LYON 1 (16)</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>CATHO</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>CATHO (2)</t>
         </is>
       </c>
       <c r="K166" t="n">
@@ -13917,22 +13917,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>LYON 1 (2)|F__LYON 2 (3)|F__VBFA2PC</t>
+          <t>SANTE (1)|F__LYON 3 (1)|F__VBFA1PB</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>VBFA2PC</t>
+          <t>VBFA1PB</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>LYON 1</t>
+          <t>SANTE</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -13942,17 +13942,17 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>LYON 1 (2)</t>
+          <t>SANTE (1)</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>LYON 2</t>
+          <t>LYON 3</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13962,7 +13962,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>LYON 2 (3)</t>
+          <t>LYON 3 (1)</t>
         </is>
       </c>
       <c r="K210" t="n">
@@ -14443,7 +14443,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SANTE (1)|F__LYON 3 (1)|F__VBFA1PB</t>
+          <t>LYON 3 (1)|F__LYON 2 (2)|F__VBFA1PB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -14453,7 +14453,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SANTE</t>
+          <t>LYON 3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -14468,17 +14468,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SANTE (1)</t>
+          <t>LYON 3 (1)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LYON 3</t>
+          <t>LYON 2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>LYON 3 (1)</t>
+          <t>LYON 2 (2)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -14553,12 +14553,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LYON 3 (1)|F__LYON 2 (2)|F__VBFA1PB</t>
+          <t>LYON 3 (3)|F__SANTE (2)|F__VBFA2PB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VBFA1PB</t>
+          <t>VBFA2PB</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -14568,7 +14568,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -14578,12 +14578,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LYON 3 (1)</t>
+          <t>LYON 3 (3)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>LYON 2</t>
+          <t>SANTE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -14598,7 +14598,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>LYON 2 (2)</t>
+          <t>SANTE (2)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -14608,44 +14608,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LYON 3 (3)|F__SANTE (2)|F__VBFA2PB</t>
+          <t>LYON 1 (2)|F__LYON 2 (3)|F__VBFA2PC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VBFA2PB</t>
+          <t>VBFA2PC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LYON 3</t>
+          <t>LYON 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>LYON 1 (2)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LYON 2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>LYON 3 (3)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>SANTE</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>F</t>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>SANTE (2)</t>
+          <t>LYON 2 (3)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -15268,7 +15268,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LYON 3 (5)|M__SANTE (5)|M__VBMA4PC</t>
+          <t>LYON 3 (5)|M__LYON 3 (6)|M__VBMA4PC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -15298,12 +15298,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SANTE</t>
+          <t>LYON 3</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -15313,7 +15313,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>SANTE (5)</t>
+          <t>LYON 3 (6)</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -15323,7 +15323,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LYON 3 (5)|M__LYON 3 (6)|M__VBMA4PC</t>
+          <t>LYON 3 (5)|M__SANTE (5)|M__VBMA4PC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -15353,12 +15353,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>LYON 3</t>
+          <t>SANTE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -15368,7 +15368,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>LYON 3 (6)</t>
+          <t>SANTE (5)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -18190,13 +18190,21 @@
           <t>ECL</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
           <t>Acad</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Score MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -18402,13 +18410,21 @@
           <t>LYON 2 HC</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>Acad</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Score MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -18669,13 +18685,21 @@
           <t>LYON 2 HC</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>Acad</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Score MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -18873,13 +18897,21 @@
           <t>LYON 2 HC</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>Acad</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Score MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -19006,13 +19038,21 @@
           <t>BESSON</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
           <t>Acad</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Score MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -19053,13 +19093,21 @@
           <t>BESSON</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr">
         <is>
           <t>Acad</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Score MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -19100,13 +19148,21 @@
           <t>BESSON</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
           <t>Acad</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Score MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -19147,13 +19203,21 @@
           <t>LAENNEC</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
           <t>Acad</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Score MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -19241,35 +19305,39 @@
           <t>BESSON</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>Acad</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Score MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>LYON 1 (7)</t>
+          <t>INSA (1)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ESSCA (1)</t>
+          <t>EXTERNE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>VBFA4PA</t>
-        </is>
-      </c>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
         <v>4</v>
       </c>
@@ -19280,51 +19348,51 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
+          <t>BESSON</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Acad</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Import MySportU</t>
-        </is>
-      </c>
+          <t>CFU</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ESME (2)</t>
+          <t>ENS (1)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ISOSTEO (1)</t>
+          <t>INSA (2)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VBFA4PB</t>
+          <t>VBMA1PB</t>
         </is>
       </c>
       <c r="E76" t="n">
         <v>4</v>
       </c>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>12/02/26</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>18:00</t>
@@ -19332,26 +19400,34 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>BESSON</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
           <t>Acad</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Score MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>INSA (1)</t>
+          <t>LYON 3 (1)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EXTERNE</t>
+          <t>LYON 2 (2)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -19359,7 +19435,11 @@
           <t>M</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VBMA1PC</t>
+        </is>
+      </c>
       <c r="E77" t="n">
         <v>4</v>
       </c>
@@ -19370,31 +19450,39 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>BESSON</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>LAENNEC</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>CFU</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
+          <t>Acad</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Score MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ENS (1)</t>
+          <t>ECL (1)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>INSA (2)</t>
+          <t>ENTPE (2)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -19404,7 +19492,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VBMA1PB</t>
+          <t>VBMA2PA</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -19417,31 +19505,39 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>BESSON</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>Acad</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Score MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>LYON 3 (1)</t>
+          <t>LYON 1 (5)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LYON 2 (2)</t>
+          <t>ISARA (1)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -19451,7 +19547,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VBMA1PC</t>
+          <t>VBMA2PB</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -19464,31 +19560,39 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>BESSON</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
           <t>Acad</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Score MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ECL (1)</t>
+          <t>ESA (1)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ENTPE (2)</t>
+          <t>CPE (1)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -19498,7 +19602,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VBMA2PA</t>
+          <t>VBMA2PD</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -19511,31 +19615,39 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>ECL</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>ESA</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
           <t>Acad</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Score MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>LYON 1 (5)</t>
+          <t>ECL (3)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ISARA (1)</t>
+          <t>LYON 1 (9)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -19545,7 +19657,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VBMA2PB</t>
+          <t>VBMA3PA</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -19558,31 +19670,39 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>BESSON</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>ECL</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
           <t>Acad</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Score MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ESA (1)</t>
+          <t>LYON 1 (20)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CPE (1)</t>
+          <t>LYON 1 (27)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -19592,7 +19712,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VBMA2PD</t>
+          <t>VBMA4PA</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -19605,31 +19725,39 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>ESA</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>BESSON</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr">
         <is>
           <t>Acad</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Score MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ECL (3)</t>
+          <t>LYON 1 (14)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LYON 1 (9)</t>
+          <t>ESME (2)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -19639,7 +19767,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VBMA3PA</t>
+          <t>VBMA4PA</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -19652,31 +19780,39 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>ECL</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>BESSON</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
           <t>Acad</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Score MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CESI (2)</t>
+          <t>LYON 1 (25)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LYON 1 (17)</t>
+          <t>ESSCA (1)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -19686,7 +19822,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VBMA3PE</t>
+          <t>VBMA4PB</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -19699,7 +19835,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -19718,12 +19854,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LYON 1 (20)</t>
+          <t>LYON 3 (5)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>LYON 1 (27)</t>
+          <t>LYON 1 (23)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -19733,7 +19869,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VBMA4PA</t>
+          <t>VBMA4PC</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -19746,12 +19882,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>LAENNEC</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -19765,35 +19901,35 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LYON 1 (14)</t>
+          <t>INSA (1)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ESME (2)</t>
+          <t>EML (1)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VBMA4PA</t>
+          <t>VBFA1PA</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>12/02/26</t>
+          <t>26/02/26</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -19812,40 +19948,40 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>LYON 1 (25)</t>
+          <t>ENS (1)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ESSCA (1)</t>
+          <t>LYON 1 (4)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VBMA4PB</t>
+          <t>VBFA2PB</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>12/02/26</t>
+          <t>26/02/26</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>DESCARTES</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -19859,30 +19995,30 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>LYON 3 (5)</t>
+          <t>LYON 3 (2)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LYON 1 (23)</t>
+          <t>LYON 1 (2)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VBMA4PC</t>
+          <t>VBFA2PC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>12/02/26</t>
+          <t>26/02/26</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -19892,7 +20028,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
+          <t>BESSON</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -19906,12 +20042,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>INSA (1)</t>
+          <t>CATHO (1)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EML (1)</t>
+          <t>LYON 1 (3)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -19921,7 +20057,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VBFA1PA</t>
+          <t>VBFA3PC</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -19934,7 +20070,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -19953,12 +20089,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ENS (1)</t>
+          <t>LYON 2 (5)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LYON 1 (4)</t>
+          <t>ECAM (1)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -19968,7 +20104,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VBFA2PB</t>
+          <t>VBFA3PA</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -19986,7 +20122,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>DESCARTES</t>
+          <t>L. J. HAUT</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -19995,17 +20131,21 @@
           <t>Acad</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Import MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>LYON 3 (2)</t>
+          <t>ESSCA (1)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LYON 1 (2)</t>
+          <t>LYON 1 (13)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -20015,7 +20155,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VBFA2PC</t>
+          <t>VBFA4PA</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -20028,12 +20168,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>L. J. HAUT</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -20042,17 +20182,21 @@
           <t>Acad</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Import MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CATHO (1)</t>
+          <t>LYON 3 (5)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LYON 1 (3)</t>
+          <t>EML (2)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -20062,7 +20206,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VBFA3PC</t>
+          <t>VBFA4PC</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -20080,7 +20224,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>LAENNEC</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -20094,22 +20238,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LYON 2 (5)</t>
+          <t>INSA (1)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ECAM (1)</t>
+          <t>LYON 1 (1)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VBFA3PA</t>
+          <t>VBMA1PA</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -20122,12 +20266,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L. J. HAUT</t>
+          <t>BESSON</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -20136,45 +20280,45 @@
           <t>Acad</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Import MySportU</t>
-        </is>
-      </c>
+      <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LYON 1 (13)</t>
+          <t>EML (1)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ESSCA (1)</t>
+          <t>ECAM (1)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VBFA4PA</t>
+          <t>VBMA1PC</t>
         </is>
       </c>
       <c r="E94" t="n">
         <v>6</v>
       </c>
-      <c r="F94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>26/02/26</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L. J. HAUT</t>
+          <t>BESSON</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -20188,22 +20332,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>LYON 3 (5)</t>
+          <t>INSA (3)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EML (2)</t>
+          <t>LYON 1 (8)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VBFA4PC</t>
+          <t>VBMA2PA</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -20216,12 +20360,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
+          <t>BESSON</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -20235,12 +20379,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>INSA (1)</t>
+          <t>LYON 1 (3)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LYON 1 (1)</t>
+          <t>INSA (4)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -20250,7 +20394,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VBMA1PA</t>
+          <t>VBMA2PB</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -20282,12 +20426,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EML (1)</t>
+          <t>LYON 3 (3)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ECAM (1)</t>
+          <t>VETO (1)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -20297,7 +20441,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VBMA1PC</t>
+          <t>VBMA2PE</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -20315,7 +20459,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>LAENNEC</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -20329,12 +20473,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>INSA (3)</t>
+          <t>LYON 1 (13)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LYON 1 (8)</t>
+          <t>INSA (6)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -20344,7 +20488,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VBMA2PA</t>
+          <t>VBMA3PA</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -20376,12 +20520,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LYON 1 (3)</t>
+          <t>LYON 1 (9)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>INSA (4)</t>
+          <t>INSA (5)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -20391,7 +20535,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VBMA2PB</t>
+          <t>VBMA3PA</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -20423,12 +20567,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LYON 3 (3)</t>
+          <t>CATHO (1)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>VETO (1)</t>
+          <t>CESI (1)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -20438,7 +20582,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VBMA2PE</t>
+          <t>VBMA3PD</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -20451,7 +20595,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -20470,12 +20614,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LYON 1 (13)</t>
+          <t>ENS (3)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>INSA (6)</t>
+          <t>EML (2)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -20485,7 +20629,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VBMA3PA</t>
+          <t>VBMA3PC</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -20498,12 +20642,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>DESCARTES</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -20517,12 +20661,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LYON 1 (9)</t>
+          <t>LYON 2 (6)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>INSA (5)</t>
+          <t>LYON 1 (12)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -20532,7 +20676,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VBMA3PA</t>
+          <t>VBMA3PC</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -20545,7 +20689,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -20564,12 +20708,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CATHO (1)</t>
+          <t>LYON 1 (27)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CESI (1)</t>
+          <t>LYON 1 (14)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -20579,7 +20723,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VBMA3PD</t>
+          <t>VBMA4PA</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -20592,12 +20736,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
+          <t>BESSON</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -20606,17 +20750,21 @@
           <t>Acad</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Import MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ENS (3)</t>
+          <t>ISOSTEO (1)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EML (2)</t>
+          <t>ESSCA (1)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -20626,7 +20774,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VBMA3PC</t>
+          <t>VBMA4PB</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -20644,7 +20792,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>DESCARTES</t>
+          <t>BESSON</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -20653,17 +20801,21 @@
           <t>Acad</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Import MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>LYON 2 (6)</t>
+          <t>SANTE (5)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LYON 1 (12)</t>
+          <t>LYON 2 (5)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -20673,7 +20825,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VBMA3PC</t>
+          <t>VBMA4PC</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -20686,12 +20838,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>LAENNEC</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -20705,28 +20857,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LYON 1 (14)</t>
+          <t>LYON 1 (11)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LYON 1 (27)</t>
+          <t>ENTPE (1)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VBMA4PA</t>
+          <t>VBFA1PA</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6</v>
-      </c>
-      <c r="F106" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>05/03/26</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr">
         <is>
           <t>14:00</t>
@@ -20748,42 +20904,42 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ESSCA (1)</t>
+          <t>EXTERNE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ISOSTEO (1)</t>
+          <t>INSA (1)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>VBMA4PB</t>
-        </is>
-      </c>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="n">
-        <v>6</v>
-      </c>
-      <c r="F107" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>05/03/26</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>CLERMONT</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Acad</t>
+          <t>CFU</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -20791,46 +20947,42 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SANTE (5)</t>
+          <t>EXTERNE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LYON 2 (5)</t>
+          <t>EXTERNE</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>VBMA4PC</t>
-        </is>
-      </c>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>26/02/26</t>
+          <t>05/03/26</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
+          <t>GRENOBLE</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Acad</t>
+          <t>CFU</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -20838,12 +20990,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>LYON 1 (11)</t>
+          <t>EML (1)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ENTPE (1)</t>
+          <t>INSA (2)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -20866,7 +21018,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -20885,12 +21037,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EXTERNE</t>
+          <t>INSA (3)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>INSA (1)</t>
+          <t>LYON 1 (5)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -20898,7 +21050,11 @@
           <t>F</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>VBFA2PA</t>
+        </is>
+      </c>
       <c r="E110" t="n">
         <v>7</v>
       </c>
@@ -20909,18 +21065,18 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>CLERMONT</t>
+          <t>BESSON</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
-          <t>CFU</t>
+          <t>Acad</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -20928,12 +21084,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EXTERNE</t>
+          <t>LYON 2 (3)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EXTERNE</t>
+          <t>VETO (1)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -20941,7 +21097,11 @@
           <t>F</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>VBFA2PC</t>
+        </is>
+      </c>
       <c r="E111" t="n">
         <v>7</v>
       </c>
@@ -20952,18 +21112,18 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>GRENOBLE</t>
+          <t>LYON 2 HC</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
-          <t>CFU</t>
+          <t>Acad</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -20971,12 +21131,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EML (1)</t>
+          <t>LYON 2 (6)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>INSA (2)</t>
+          <t>ECL (1)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -20986,7 +21146,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VBFA1PA</t>
+          <t>VBFA2PA</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -20999,12 +21159,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>LYON 2 HC</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -21018,12 +21178,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>INSA (3)</t>
+          <t>LYON 1 (6)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>LYON 1 (5)</t>
+          <t>LYON 3 (4)</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -21033,7 +21193,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VBFA2PA</t>
+          <t>VBFA3PB</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -21046,7 +21206,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -21065,12 +21225,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>LYON 2 (3)</t>
+          <t>LYON 1 (7)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>VETO (1)</t>
+          <t>LYON 1 (12)</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -21080,7 +21240,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VBFA2PC</t>
+          <t>VBFA4PA</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -21093,12 +21253,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>LYON 2 HC</t>
+          <t>BESSON</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -21112,12 +21272,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>LYON 2 (6)</t>
+          <t>ESSCA (1)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ECL (1)</t>
+          <t>ECL (2)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -21127,7 +21287,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VBFA2PA</t>
+          <t>VBFA4PA</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -21140,12 +21300,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>LYON 2 HC</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -21159,12 +21319,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>LYON 1 (6)</t>
+          <t>ESME (2)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LYON 3 (4)</t>
+          <t>ISOSTEO (1)</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -21174,25 +21334,21 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VBFA3PB</t>
+          <t>VBFA4PB</t>
         </is>
       </c>
       <c r="E116" t="n">
         <v>7</v>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>05/03/26</t>
-        </is>
-      </c>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>LYON 2 HC</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -21206,12 +21362,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>LYON 1 (7)</t>
+          <t>ESA (2)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LYON 1 (12)</t>
+          <t>LYON 3 (6)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -21221,7 +21377,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VBFA4PA</t>
+          <t>VBFA4PC</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -21234,12 +21390,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>L. J. HAUT</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -21253,24 +21409,20 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ESSCA (1)</t>
+          <t>EXTERNE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ECL (2)</t>
+          <t>INSA (1)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>VBFA4PA</t>
-        </is>
-      </c>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="n">
         <v>7</v>
       </c>
@@ -21281,18 +21433,18 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>GRENOBLE</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Acad</t>
+          <t>CFU</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -21300,22 +21452,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ESA (2)</t>
+          <t>INSA (2)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>LYON 3 (6)</t>
+          <t>LYON 2 (1)</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VBFA4PC</t>
+          <t>VBMA1PB</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -21328,12 +21480,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
+          <t>BESSON</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -21347,12 +21499,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>EXTERNE</t>
+          <t>ECL (2)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>INSA (1)</t>
+          <t>ENTPE (2)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -21360,7 +21512,11 @@
           <t>M</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VBMA2PA</t>
+        </is>
+      </c>
       <c r="E120" t="n">
         <v>7</v>
       </c>
@@ -21371,18 +21527,18 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>GRENOBLE</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
-          <t>CFU</t>
+          <t>Acad</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -21390,12 +21546,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>INSA (2)</t>
+          <t>ESA (1)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>LYON 2 (1)</t>
+          <t>SANTE (1)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -21405,7 +21561,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VBMA1PB</t>
+          <t>VBMA2PD</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -21418,12 +21574,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>ESA</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -21437,12 +21593,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>LYON 1 (2)</t>
+          <t>LYON 2 (IEP) (4)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ENS (1)</t>
+          <t>VETO (1)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -21452,7 +21608,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VBMA1PB</t>
+          <t>VBMA2PE</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -21465,12 +21621,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>DESCARTES</t>
+          <t>LYON 2 HC</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -21484,12 +21640,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ECL (2)</t>
+          <t>LYON 3 (2)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ENTPE (2)</t>
+          <t>CPE (1)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -21499,7 +21655,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VBMA2PA</t>
+          <t>VBMA2PD</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -21512,12 +21668,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>LAENNEC</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -21531,12 +21687,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ESA (1)</t>
+          <t>SANTE (2)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SANTE (1)</t>
+          <t>LYON 1 (21)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -21546,7 +21702,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VBMA2PD</t>
+          <t>VBMA2PE</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -21564,7 +21720,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>ESA</t>
+          <t>LAENNEC</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -21578,12 +21734,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>LYON 2 (IEP) (4)</t>
+          <t>LYON 1 (15)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>VETO (1)</t>
+          <t>LYON 1 (22)</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -21593,7 +21749,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VBMA2PE</t>
+          <t>VBMA3PD</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -21606,12 +21762,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>LYON 2 HC</t>
+          <t>BESSON</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -21625,12 +21781,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>LYON 3 (2)</t>
+          <t>CATHO (2)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CPE (1)</t>
+          <t>LYON 3 (4)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -21640,7 +21796,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VBMA2PD</t>
+          <t>VBMA3PF</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -21672,12 +21828,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SANTE (2)</t>
+          <t>CESI (2)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>LYON 1 (21)</t>
+          <t>LYON 1 (17)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -21687,7 +21843,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VBMA2PE</t>
+          <t>VBMA3PE</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -21714,17 +21870,21 @@
           <t>Acad</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Import MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>LYON 1 (15)</t>
+          <t>LYON 1 (16)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>LYON 1 (22)</t>
+          <t>SANTE (4)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -21734,7 +21894,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VBMA3PD</t>
+          <t>VBMA3PF</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -21747,7 +21907,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -21766,12 +21926,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CATHO (2)</t>
+          <t>LYON 1 (19)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>LYON 3 (4)</t>
+          <t>ISOSTEO (1)</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -21781,7 +21941,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VBMA3PF</t>
+          <t>VBMA4PB</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -21794,12 +21954,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
+          <t>BESSON</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -21813,35 +21973,35 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>LYON 1 (16)</t>
+          <t>LYON 1 (1)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SANTE (4)</t>
+          <t>INSA (1)</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VBMA3PF</t>
+          <t>VBFA1PA</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>05/03/26</t>
+          <t>12/03/26</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -21860,40 +22020,40 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>LYON 1 (19)</t>
+          <t>ESA (1)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ISOSTEO (1)</t>
+          <t>SANTE (1)</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VBMA4PB</t>
+          <t>VBFA1PB</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>05/03/26</t>
+          <t>12/03/26</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>LAENNEC</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -21907,12 +22067,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>LYON 1 (1)</t>
+          <t>LYON 3 (2)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>INSA (1)</t>
+          <t>VETO (1)</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -21922,7 +22082,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VBFA1PA</t>
+          <t>VBFA2PC</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -21935,12 +22095,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>L. J. HAUT</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -21949,17 +22109,21 @@
           <t>Acad</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Import MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ESA (1)</t>
+          <t>CPE (1)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SANTE (1)</t>
+          <t>SANTE (4)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -21969,7 +22133,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VBFA1PB</t>
+          <t>VBFA3PB</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -22001,12 +22165,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>LYON 3 (2)</t>
+          <t>LYON 1 (3)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>VETO (1)</t>
+          <t>LYON 2 (7)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -22016,7 +22180,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VBFA2PC</t>
+          <t>VBFA3PC</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -22034,7 +22198,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>L. J. HAUT</t>
+          <t>BESSON</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -22043,21 +22207,17 @@
           <t>Acad</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>Import MySportU</t>
-        </is>
-      </c>
+      <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CPE (1)</t>
+          <t>SANTE (3)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SANTE (4)</t>
+          <t>LYON 2 (IEP) (4)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -22067,7 +22227,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VBFA3PB</t>
+          <t>VBFA3PC</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -22099,12 +22259,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>LYON 1 (3)</t>
+          <t>LYON 1 (7)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>LYON 2 (7)</t>
+          <t>ESSCA (1)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -22114,25 +22274,21 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VBFA3PC</t>
+          <t>VBFA4PA</t>
         </is>
       </c>
       <c r="E136" t="n">
         <v>8</v>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>12/03/26</t>
-        </is>
-      </c>
+      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>LYON 2 HC</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -22146,12 +22302,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SANTE (3)</t>
+          <t>LYON 1 (10)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>LYON 2 (IEP) (4)</t>
+          <t>ISOSTEO (1)</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -22161,7 +22317,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VBFA3PC</t>
+          <t>VBFA4PB</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -22174,12 +22330,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
+          <t>BESSON</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -22193,12 +22349,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>LYON 1 (10)</t>
+          <t>LYON 1 (8)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ISOSTEO (1)</t>
+          <t>ESME (2)</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -22240,22 +22396,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>LYON 1 (8)</t>
+          <t>ENTPE (1)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ESME (2)</t>
+          <t>INSA (1)</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VBFA4PB</t>
+          <t>VBMA1PA</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -22268,7 +22424,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -22287,12 +22443,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ENTPE (1)</t>
+          <t>LYON 1 (26)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>INSA (1)</t>
+          <t>LYON 1 (1)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -22334,12 +22490,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>LYON 1 (26)</t>
+          <t>LYON 1 (2)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>LYON 1 (1)</t>
+          <t>ENS (1)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -22349,7 +22505,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VBMA1PA</t>
+          <t>VBMA1PB</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -22362,12 +22518,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>DESCARTES</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -22376,7 +22532,11 @@
           <t>Acad</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>MAJ MySportU: Date: 05/03/26→12/03/26, Sem: 7 (05/03)→8 (12/03)</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -22812,12 +22972,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
+          <t>LYON 1 (11)</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
           <t>LYON 1 (1)</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>LYON 1 (11)</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -22833,7 +22993,11 @@
       <c r="E151" t="n">
         <v>9</v>
       </c>
-      <c r="F151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>19/03/26</t>
+        </is>
+      </c>
       <c r="G151" t="inlineStr">
         <is>
           <t>14:00</t>
@@ -22850,7 +23014,11 @@
           <t>Acad</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Import MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -23491,7 +23659,11 @@
       <c r="E165" t="n">
         <v>9</v>
       </c>
-      <c r="F165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>19/03/26</t>
+        </is>
+      </c>
       <c r="G165" t="inlineStr">
         <is>
           <t>18:00</t>
@@ -23508,7 +23680,11 @@
           <t>Acad</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Import MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -23560,12 +23736,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CESI (2)</t>
+          <t>CATHO (2)</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SANTE (3)</t>
+          <t>LYON 1 (16)</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -23575,7 +23751,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VBMA3PE</t>
+          <t>VBMA3PF</t>
         </is>
       </c>
       <c r="E167" t="n">
@@ -23593,7 +23769,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>LAENNEC</t>
+          <t>L. J. HAUT</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -23602,17 +23778,21 @@
           <t>Acad</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Import MySportU</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ECAM (2)</t>
+          <t>CESI (2)</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>LYON 1 (17)</t>
+          <t>SANTE (3)</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -23640,7 +23820,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>BESSON</t>
+          <t>LAENNEC</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -23654,12 +23834,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>LYON 1 (16)</t>
+          <t>ECAM (2)</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CATHO (2)</t>
+          <t>LYON 1 (17)</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -23669,13 +23849,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VBMA3PF</t>
+          <t>VBMA3PE</t>
         </is>
       </c>
       <c r="E169" t="n">
         <v>9</v>
       </c>
-      <c r="F169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>19/03/26</t>
+        </is>
+      </c>
       <c r="G169" t="inlineStr">
         <is>
           <t>20:00</t>
@@ -23683,7 +23867,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>L. J. HAUT</t>
+          <t>BESSON</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -24637,12 +24821,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>LYON 1 (2)</t>
+          <t>SANTE (1)</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>LYON 2 (3)</t>
+          <t>LYON 3 (1)</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -24652,13 +24836,17 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VBFA2PC</t>
+          <t>VBFA1PB</t>
         </is>
       </c>
       <c r="E190" t="n">
         <v>11</v>
       </c>
-      <c r="F190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>02/04/26</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr">
         <is>
           <t>20:00</t>
@@ -24675,7 +24863,11 @@
           <t>Acad</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>MAJ MySportU: Gym: ENTENTE→LAENNEC, Date: 22/01/26→02/04/26, Heure: ?→20:00, Sem: 1 (22/01)→11 (02/04)</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -25922,7 +26114,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19131723.00</t>
+          <t>4722895.00</t>
         </is>
       </c>
     </row>
